--- a/tables/AttenuatorDiconPassportCut.xlsx
+++ b/tables/AttenuatorDiconPassportCut.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB46D643-04B8-4B44-994F-AA5E9AD95F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3122CA-B467-4C33-AD5E-692E6C2D7A81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>Attenuation_dBm</t>
+    <t>Voltage_V</t>
   </si>
   <si>
-    <t>Voltage_V</t>
+    <t>Attenuation_dB</t>
   </si>
 </sst>
 </file>
@@ -353,20 +353,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B123"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>0.372</v>
       </c>
@@ -374,7 +374,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>0.374</v>
       </c>
@@ -382,7 +382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>0.378</v>
       </c>
@@ -390,7 +390,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>0.38500000000000001</v>
       </c>
@@ -398,7 +398,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>0.39600000000000002</v>
       </c>
@@ -406,7 +406,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>0.40899999999999997</v>
       </c>
@@ -414,7 +414,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>0.42499999999999999</v>
       </c>
@@ -422,7 +422,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>0.44600000000000001</v>
       </c>
@@ -430,7 +430,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>0.47099999999999997</v>
       </c>
@@ -438,7 +438,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>0.502</v>
       </c>
@@ -446,7 +446,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>0.53600000000000003</v>
       </c>
@@ -454,7 +454,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>0.57499999999999996</v>
       </c>
@@ -462,7 +462,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>0.62</v>
       </c>
@@ -470,7 +470,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>0.67100000000000004</v>
       </c>
@@ -478,7 +478,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>0.72799999999999998</v>
       </c>
@@ -486,7 +486,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>0.79300000000000004</v>
       </c>
@@ -494,7 +494,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>0.86499999999999999</v>
       </c>
@@ -502,7 +502,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>0.94299999999999995</v>
       </c>
@@ -510,7 +510,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>1.03</v>
       </c>
@@ -518,7 +518,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>1.1259999999999999</v>
       </c>
@@ -526,7 +526,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>1.2310000000000001</v>
       </c>
@@ -534,7 +534,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>1.3460000000000001</v>
       </c>
@@ -542,7 +542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>1.468</v>
       </c>
@@ -550,7 +550,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>1.6020000000000001</v>
       </c>
@@ -558,7 +558,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>1.7490000000000001</v>
       </c>
@@ -566,7 +566,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>1.905</v>
       </c>
@@ -574,7 +574,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>2.0710000000000002</v>
       </c>
@@ -582,7 +582,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>2.2519999999999998</v>
       </c>
@@ -590,7 +590,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>2.4409999999999998</v>
       </c>
@@ -598,7 +598,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>2.6459999999999999</v>
       </c>
@@ -606,7 +606,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>2.8620000000000001</v>
       </c>
@@ -614,7 +614,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>3.093</v>
       </c>
@@ -622,7 +622,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>3.3380000000000001</v>
       </c>
@@ -630,7 +630,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>3.597</v>
       </c>
@@ -638,7 +638,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>3.871</v>
       </c>
@@ -646,7 +646,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>4.1609999999999996</v>
       </c>
@@ -654,7 +654,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>4.4669999999999996</v>
       </c>
@@ -662,7 +662,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>4.7889999999999997</v>
       </c>
@@ -670,7 +670,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>5.1260000000000003</v>
       </c>
@@ -678,7 +678,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>5.4790000000000001</v>
       </c>
@@ -686,7 +686,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>5.851</v>
       </c>
@@ -694,7 +694,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>6.2389999999999999</v>
       </c>
@@ -702,7 +702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>6.6429999999999998</v>
       </c>
@@ -710,7 +710,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>7.0640000000000001</v>
       </c>
@@ -718,7 +718,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>7.5039999999999996</v>
       </c>
@@ -726,7 +726,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>7.9589999999999996</v>
       </c>
@@ -734,7 +734,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>8.4339999999999993</v>
       </c>
@@ -742,7 +742,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>8.9239999999999995</v>
       </c>
@@ -750,7 +750,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>9.43</v>
       </c>
@@ -758,7 +758,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>9.9670000000000005</v>
       </c>
@@ -766,7 +766,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>10.51</v>
       </c>
@@ -774,7 +774,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>11.071</v>
       </c>
@@ -782,7 +782,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>11.648</v>
       </c>
@@ -790,7 +790,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>12.241</v>
       </c>
@@ -798,7 +798,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>12.852</v>
       </c>
@@ -806,7 +806,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>13.476000000000001</v>
       </c>
@@ -814,7 +814,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>14.117000000000001</v>
       </c>
@@ -822,7 +822,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>14.773</v>
       </c>
@@ -830,7 +830,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>15.449</v>
       </c>
@@ -838,7 +838,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>16.138999999999999</v>
       </c>
@@ -846,7 +846,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>16.841000000000001</v>
       </c>
@@ -854,7 +854,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>17.556999999999999</v>
       </c>
@@ -862,7 +862,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>18.294</v>
       </c>
@@ -870,7 +870,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>19.041</v>
       </c>
@@ -878,7 +878,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>19.809999999999999</v>
       </c>
@@ -886,7 +886,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>20.597999999999999</v>
       </c>
@@ -894,7 +894,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>21.402000000000001</v>
       </c>
@@ -902,7 +902,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>22.236000000000001</v>
       </c>
@@ -910,7 +910,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>23.085000000000001</v>
       </c>
@@ -918,7 +918,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>23.966000000000001</v>
       </c>
@@ -926,7 +926,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>24.87</v>
       </c>
@@ -934,7 +934,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>25.812999999999999</v>
       </c>
@@ -942,7 +942,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>26.795000000000002</v>
       </c>
@@ -950,7 +950,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>27.82</v>
       </c>
@@ -958,7 +958,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>28.895</v>
       </c>
@@ -966,7 +966,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>30.033000000000001</v>
       </c>
@@ -974,7 +974,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>31.231000000000002</v>
       </c>
@@ -982,7 +982,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>32.503</v>
       </c>
@@ -990,7 +990,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>33.866</v>
       </c>
@@ -998,7 +998,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>35.325000000000003</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>36.898000000000003</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>38.621000000000002</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>40.515999999999998</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>42.628</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>45.014000000000003</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>47.777000000000001</v>
       </c>
@@ -1054,147 +1054,147 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
     </row>
